--- a/Tests/Validation/Wheat/data/FAR DMC W20-05.xlsx
+++ b/Tests/Validation/Wheat/data/FAR DMC W20-05.xlsx
@@ -1,32 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Observed" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Observed" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,16 +48,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -417,126 +430,111 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>SimulationName</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>Clock.Today</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Phenology.CurrentStageName</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Wheat.SowingData.Cultivar</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Grazed</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Potential</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Wheat.AboveGround.Wt.se</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Spike.HeadNumber.se</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Leaf.StemPopulation.se</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>NDVIModel.Script.NDVI.se</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Density.se</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>Wheat.Grain.Moisture</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Wheat.Grain.WaterContent</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Moisture.se</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Protein.se</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Screenings.se</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Wheat.Grain.Wt.se</t>
         </is>
@@ -548,37 +546,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>0.6641625</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.0184553679521704</v>
+      </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>0.6641625</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.0184553679521704</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -586,9 +572,6 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -596,37 +579,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>0.879825</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0083965394657561</v>
+      </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="n">
-        <v>0.879825</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.0083965394657561</v>
-      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -634,9 +605,6 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -644,37 +612,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>0.9038675</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.00867144872075401</v>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="n">
-        <v>0.9038675</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.00867144872075401</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -682,9 +638,6 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,37 +645,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>0.912925</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.010613714791093</v>
+      </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>0.912925</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.010613714791093</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -730,9 +671,6 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -740,37 +678,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>0.8558875</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.00956083275225891</v>
+      </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="n">
-        <v>0.8558875</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.00956083275225891</v>
-      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -778,9 +704,6 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -788,37 +711,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>0.7309025</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.00524855595219611</v>
+      </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="n">
-        <v>0.7309025</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.00524855595219611</v>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -826,9 +737,6 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -836,7 +744,7 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C8" t="inlineStr">
@@ -844,33 +752,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0.617605</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0420451274426261</v>
+      </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="n">
-        <v>0.617605</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.0420451274426261</v>
-      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -878,9 +774,6 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -888,7 +781,7 @@
           <t>FAR DMC W20-05GrazedGS32-33CvTrojan</t>
         </is>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C9" t="inlineStr">
@@ -896,65 +789,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D9" t="n">
+        <v>1663.69880952919</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.660085003091025</v>
+      </c>
+      <c r="F9" t="n">
+        <v>399.439939291829</v>
       </c>
       <c r="G9" t="n">
-        <v>1663.69880952919</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.660085003091025</v>
-      </c>
-      <c r="I9" t="n">
-        <v>399.439939291829</v>
-      </c>
-      <c r="J9" t="n">
         <v>19.2426640461686</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="L9" t="n">
+        <v>72.758</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.855792030811226</v>
+      </c>
+      <c r="N9" t="n">
+        <v>12.275</v>
+      </c>
       <c r="O9" t="n">
-        <v>72.758</v>
+        <v>0.137689263682152</v>
       </c>
       <c r="P9" t="n">
-        <v>0.855792030811226</v>
+        <v>12.45</v>
       </c>
       <c r="Q9" t="n">
-        <v>12.275</v>
+        <v>0.13228756555323</v>
       </c>
       <c r="R9" t="n">
-        <v>0.137689263682152</v>
+        <v>6.555</v>
       </c>
       <c r="S9" t="n">
-        <v>12.45</v>
+        <v>0.5217678283170269</v>
       </c>
       <c r="T9" t="n">
-        <v>0.13228756555323</v>
+        <v>627.896995704281</v>
       </c>
       <c r="U9" t="n">
-        <v>6.555</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0.5217678283170269</v>
-      </c>
-      <c r="W9" t="n">
-        <v>627.896995704281</v>
-      </c>
-      <c r="X9" t="n">
         <v>0.187674731913257</v>
       </c>
     </row>
@@ -964,33 +842,25 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0.832645</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0218540265168687</v>
+      </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>0.832645</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.0218540265168687</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -998,9 +868,6 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1008,33 +875,25 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0.905875</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.00622699700230107</v>
+      </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="n">
-        <v>0.905875</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.00622699700230107</v>
-      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1042,9 +901,6 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1052,33 +908,25 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+      <c r="J12" t="n">
+        <v>0.92631</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.00489031185099682</v>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="n">
-        <v>0.92631</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.00489031185099682</v>
-      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1086,9 +934,6 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1096,33 +941,25 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="n">
+        <v>0.9143225</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.00901535853881218</v>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="n">
-        <v>0.9143225</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.00901535853881218</v>
-      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1130,9 +967,6 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1140,33 +974,25 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="n">
+        <v>0.8678399999999999</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.00667479213159479</v>
+      </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="n">
-        <v>0.8678399999999999</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.00667479213159479</v>
-      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1174,9 +1000,6 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1184,33 +1007,25 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>0.73394</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.0225615716798867</v>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="n">
-        <v>0.73394</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.0225615716798867</v>
-      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1218,9 +1033,6 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1228,7 +1040,7 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C16" t="inlineStr">
@@ -1236,29 +1048,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="n">
+        <v>0.595225</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0502687804871639</v>
+      </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="n">
-        <v>0.595225</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.0502687804871639</v>
-      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1266,9 +1070,6 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
-      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1276,7 +1077,7 @@
           <t>FAR DMC W20-05GrazedNoneCvTrojan</t>
         </is>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -1284,61 +1085,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D17" t="n">
+        <v>1617.4304181633</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.19578531017157</v>
+      </c>
+      <c r="F17" t="n">
+        <v>407.973335226618</v>
       </c>
       <c r="G17" t="n">
-        <v>1617.4304181633</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1.19578531017157</v>
-      </c>
-      <c r="I17" t="n">
-        <v>407.973335226618</v>
-      </c>
-      <c r="J17" t="n">
         <v>23.0453723997451</v>
       </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="L17" t="n">
+        <v>73.304</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.478076005114944</v>
+      </c>
+      <c r="N17" t="n">
+        <v>12.425</v>
+      </c>
       <c r="O17" t="n">
-        <v>73.304</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="P17" t="n">
-        <v>0.478076005114944</v>
+        <v>12.55</v>
       </c>
       <c r="Q17" t="n">
-        <v>12.425</v>
+        <v>0.104083299973307</v>
       </c>
       <c r="R17" t="n">
-        <v>0.110867789130417</v>
+        <v>6.225</v>
       </c>
       <c r="S17" t="n">
-        <v>12.55</v>
+        <v>1.27612368784012</v>
       </c>
       <c r="T17" t="n">
-        <v>0.104083299973307</v>
+        <v>630.2861762237389</v>
       </c>
       <c r="U17" t="n">
-        <v>6.225</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.27612368784012</v>
-      </c>
-      <c r="W17" t="n">
-        <v>630.2861762237389</v>
-      </c>
-      <c r="X17" t="n">
         <v>0.231294779345749</v>
       </c>
     </row>
@@ -1348,37 +1138,25 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="n">
+        <v>0.8263575</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.018141385639379</v>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="n">
-        <v>0.8263575</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.018141385639379</v>
-      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -1386,9 +1164,6 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
-      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1396,37 +1171,25 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="J19" t="n">
+        <v>0.7277925</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.0134447241046442</v>
+      </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>0.7277925</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.0134447241046442</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -1434,9 +1197,6 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
-      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1444,37 +1204,25 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
+      <c r="J20" t="n">
+        <v>0.7953525</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.0144606543045834</v>
+      </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="n">
-        <v>0.7953525</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0.0144606543045834</v>
-      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1482,9 +1230,6 @@
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
-      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1492,37 +1237,25 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="n">
+        <v>0.8868025</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.00656947660903568</v>
+      </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="n">
-        <v>0.8868025</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.00656947660903568</v>
-      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1530,9 +1263,6 @@
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
-      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1540,37 +1270,25 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="J22" t="n">
+        <v>0.8591075</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.00110139589461132</v>
+      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>0.8591075</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.00110139589461132</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -1578,9 +1296,6 @@
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
-      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1588,37 +1303,25 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="n">
+        <v>0.579255</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.0227374223473111</v>
+      </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="n">
-        <v>0.579255</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0.0227374223473111</v>
-      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -1626,9 +1329,6 @@
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
-      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1636,7 +1336,7 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C24" t="inlineStr">
@@ -1644,33 +1344,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="n">
+        <v>0.5997275</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.027100346976561</v>
+      </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="n">
-        <v>0.5997275</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0.027100346976561</v>
-      </c>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -1678,9 +1366,6 @@
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
-      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1688,7 +1373,7 @@
           <t>FAR DMC W20-05GrazedGS22CvTrojan</t>
         </is>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C25" t="inlineStr">
@@ -1696,65 +1381,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D25" t="n">
+        <v>1317.71014677737</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.758659075259435</v>
+      </c>
+      <c r="F25" t="n">
+        <v>500.870089479606</v>
       </c>
       <c r="G25" t="n">
-        <v>1317.71014677737</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.758659075259435</v>
-      </c>
-      <c r="I25" t="n">
-        <v>500.870089479606</v>
-      </c>
-      <c r="J25" t="n">
         <v>55.2746435776834</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>74.71599999999999</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.469184398717604</v>
+      </c>
+      <c r="N25" t="n">
+        <v>12.575</v>
+      </c>
       <c r="O25" t="n">
-        <v>74.71599999999999</v>
+        <v>0.103077640640442</v>
       </c>
       <c r="P25" t="n">
-        <v>0.469184398717604</v>
+        <v>12.125</v>
       </c>
       <c r="Q25" t="n">
-        <v>12.575</v>
+        <v>0.165201896679992</v>
       </c>
       <c r="R25" t="n">
-        <v>0.103077640640442</v>
+        <v>5.865</v>
       </c>
       <c r="S25" t="n">
-        <v>12.125</v>
+        <v>0.299819390077871</v>
       </c>
       <c r="T25" t="n">
-        <v>0.165201896679992</v>
+        <v>464.06756515775</v>
       </c>
       <c r="U25" t="n">
-        <v>5.865</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0.299819390077871</v>
-      </c>
-      <c r="W25" t="n">
-        <v>464.06756515775</v>
-      </c>
-      <c r="X25" t="n">
         <v>0.146485296658531</v>
       </c>
     </row>
@@ -1764,37 +1434,25 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="n">
+        <v>0.556305</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0522108543152986</v>
+      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>0.556305</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0.0522108543152986</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -1802,9 +1460,6 @@
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
-      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1812,37 +1467,25 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="J27" t="n">
+        <v>0.8972475</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.00290634184442689</v>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="n">
-        <v>0.8972475</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0.00290634184442689</v>
-      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -1850,9 +1493,6 @@
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1860,37 +1500,25 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="J28" t="n">
+        <v>0.9137</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.00668962505177482</v>
+      </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="n">
-        <v>0.9137</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0.00668962505177482</v>
-      </c>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -1898,9 +1526,6 @@
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
-      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1908,37 +1533,25 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="n">
+        <v>0.9198875</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.0123706712125899</v>
+      </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="n">
-        <v>0.9198875</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.0123706712125899</v>
-      </c>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -1946,9 +1559,6 @@
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1956,37 +1566,25 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="n">
+        <v>0.867345</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.00785262323473288</v>
+      </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="n">
-        <v>0.867345</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.00785262323473288</v>
-      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -1994,9 +1592,6 @@
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2004,37 +1599,25 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="n">
+        <v>0.705885</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.00898277379209785</v>
+      </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="n">
-        <v>0.705885</v>
-      </c>
-      <c r="N31" t="n">
-        <v>0.00898277379209785</v>
-      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -2042,9 +1625,6 @@
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2052,7 +1632,7 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C32" t="inlineStr">
@@ -2060,33 +1640,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
+      <c r="J32" t="n">
+        <v>0.6342025</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.0326511925190592</v>
+      </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="n">
-        <v>0.6342025</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.0326511925190592</v>
-      </c>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -2094,9 +1662,6 @@
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2104,7 +1669,7 @@
           <t>FAR DMC W20-05GrazedGS30CvTrojan</t>
         </is>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C33" t="inlineStr">
@@ -2112,65 +1677,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Trojan</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D33" t="n">
+        <v>1555.5659461147</v>
+      </c>
+      <c r="E33" t="n">
+        <v>3.03079606986776</v>
+      </c>
+      <c r="F33" t="n">
+        <v>403.82778076596</v>
       </c>
       <c r="G33" t="n">
-        <v>1555.5659461147</v>
-      </c>
-      <c r="H33" t="n">
-        <v>3.03079606986776</v>
-      </c>
-      <c r="I33" t="n">
-        <v>403.82778076596</v>
-      </c>
-      <c r="J33" t="n">
         <v>104.024360245953</v>
       </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>71.218</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.472141927814082</v>
+      </c>
+      <c r="N33" t="n">
+        <v>11.925</v>
+      </c>
       <c r="O33" t="n">
-        <v>71.218</v>
+        <v>0.0249999999999997</v>
       </c>
       <c r="P33" t="n">
-        <v>0.472141927814082</v>
+        <v>12.275</v>
       </c>
       <c r="Q33" t="n">
-        <v>11.925</v>
+        <v>0.110867789130417</v>
       </c>
       <c r="R33" t="n">
-        <v>0.0249999999999997</v>
+        <v>6.1475</v>
       </c>
       <c r="S33" t="n">
-        <v>12.275</v>
+        <v>0.493514184193322</v>
       </c>
       <c r="T33" t="n">
-        <v>0.110867789130417</v>
+        <v>593.888679517724</v>
       </c>
       <c r="U33" t="n">
-        <v>6.1475</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0.493514184193322</v>
-      </c>
-      <c r="W33" t="n">
-        <v>593.888679517724</v>
-      </c>
-      <c r="X33" t="n">
         <v>0.121992025192789</v>
       </c>
     </row>
@@ -2180,37 +1730,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="n">
+        <v>0.8379025</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.00821668056962988</v>
+      </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="n">
-        <v>0.8379025</v>
-      </c>
-      <c r="N34" t="n">
-        <v>0.00821668056962988</v>
-      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -2218,9 +1756,6 @@
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
       <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2228,37 +1763,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="n">
+        <v>0.8977825</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.00488968365541165</v>
+      </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="n">
-        <v>0.8977825</v>
-      </c>
-      <c r="N35" t="n">
-        <v>0.00488968365541165</v>
-      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -2266,9 +1789,6 @@
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
       <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
-      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2276,37 +1796,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="n">
+        <v>0.5902674999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.0229606403710785</v>
+      </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="n">
-        <v>0.5902674999999999</v>
-      </c>
-      <c r="N36" t="n">
-        <v>0.0229606403710785</v>
-      </c>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr"/>
       <c r="Q36" t="inlineStr"/>
@@ -2314,9 +1822,6 @@
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
       <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
-      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2324,37 +1829,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="J37" t="n">
+        <v>0.80298</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.0221876921587923</v>
+      </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="n">
-        <v>0.80298</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0.0221876921587923</v>
-      </c>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr"/>
       <c r="Q37" t="inlineStr"/>
@@ -2362,9 +1855,6 @@
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2372,37 +1862,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="J38" t="n">
+        <v>0.8126725</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0101076764350995</v>
+      </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="n">
-        <v>0.8126725</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.0101076764350995</v>
-      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr"/>
       <c r="Q38" t="inlineStr"/>
@@ -2410,9 +1888,6 @@
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
-      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2420,37 +1895,25 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="n">
+        <v>0.7548825</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0221191490851253</v>
+      </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="n">
-        <v>0.7548825</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.0221191490851253</v>
-      </c>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr"/>
       <c r="Q39" t="inlineStr"/>
@@ -2458,9 +1921,6 @@
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
       <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2468,7 +1928,7 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C40" t="inlineStr">
@@ -2476,33 +1936,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="n">
+        <v>0.7427175</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.0228328919817442</v>
+      </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="n">
-        <v>0.7427175</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.0228328919817442</v>
-      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr"/>
       <c r="Q40" t="inlineStr"/>
@@ -2510,9 +1958,6 @@
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
       <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
-      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2520,7 +1965,7 @@
           <t>FAR DMC W20-05GrazedGS32-33CvAccroc</t>
         </is>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C41" t="inlineStr">
@@ -2528,65 +1973,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>GS32-33</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D41" t="n">
+        <v>1648.42909463012</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2.70929712082438</v>
+      </c>
+      <c r="F41" t="n">
+        <v>542.1536974165469</v>
       </c>
       <c r="G41" t="n">
-        <v>1648.42909463012</v>
-      </c>
-      <c r="H41" t="n">
-        <v>2.70929712082438</v>
-      </c>
-      <c r="I41" t="n">
-        <v>542.1536974165469</v>
-      </c>
-      <c r="J41" t="n">
         <v>98.23712336797961</v>
       </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>75.76349999999999</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.283868954507764</v>
+      </c>
+      <c r="N41" t="n">
+        <v>12.025</v>
+      </c>
       <c r="O41" t="n">
-        <v>75.76349999999999</v>
+        <v>0.0853912563829963</v>
       </c>
       <c r="P41" t="n">
-        <v>0.283868954507764</v>
+        <v>10.925</v>
       </c>
       <c r="Q41" t="n">
-        <v>12.025</v>
+        <v>0.368272996566406</v>
       </c>
       <c r="R41" t="n">
-        <v>0.0853912563829963</v>
+        <v>5.33</v>
       </c>
       <c r="S41" t="n">
-        <v>10.925</v>
+        <v>0.341076726460973</v>
       </c>
       <c r="T41" t="n">
-        <v>0.368272996566406</v>
+        <v>642.556353151397</v>
       </c>
       <c r="U41" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0.341076726460973</v>
-      </c>
-      <c r="W41" t="n">
-        <v>642.556353151397</v>
-      </c>
-      <c r="X41" t="n">
         <v>0.205018236364791</v>
       </c>
     </row>
@@ -2596,33 +2026,25 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
+      <c r="J42" t="n">
+        <v>0.8418099999999999</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.00898995735992854</v>
+      </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="n">
-        <v>0.8418099999999999</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.00898995735992854</v>
-      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr"/>
       <c r="Q42" t="inlineStr"/>
@@ -2630,9 +2052,6 @@
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
       <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
-      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2640,33 +2059,25 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="n">
+        <v>0.9065175</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.00273559979711946</v>
+      </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="n">
-        <v>0.9065175</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.00273559979711946</v>
-      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
       <c r="P43" t="inlineStr"/>
       <c r="Q43" t="inlineStr"/>
@@ -2674,9 +2085,6 @@
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
       <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
-      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2684,33 +2092,25 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
+      <c r="J44" t="n">
+        <v>0.922675</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.00626689516427394</v>
+      </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="n">
-        <v>0.922675</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.00626689516427394</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr"/>
       <c r="Q44" t="inlineStr"/>
@@ -2718,9 +2118,6 @@
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
       <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2728,33 +2125,25 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0.92691</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.0122372144161434</v>
+      </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="n">
-        <v>0.92691</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.0122372144161434</v>
-      </c>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr"/>
       <c r="Q45" t="inlineStr"/>
@@ -2762,9 +2151,6 @@
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
       <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
-      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2772,33 +2158,25 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>0.8722425</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.0109003229118835</v>
+      </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="n">
-        <v>0.8722425</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.0109003229118835</v>
-      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr"/>
       <c r="Q46" t="inlineStr"/>
@@ -2806,9 +2184,6 @@
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
       <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
-      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2816,33 +2191,25 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="n">
+        <v>0.7969349999999999</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.0247255544258701</v>
+      </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="n">
-        <v>0.7969349999999999</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.0247255544258701</v>
-      </c>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr"/>
       <c r="Q47" t="inlineStr"/>
@@ -2850,9 +2217,6 @@
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
       <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2860,7 +2224,7 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C48" t="inlineStr">
@@ -2868,29 +2232,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="J48" t="n">
+        <v>0.6965725</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.0339076307476159</v>
+      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
-        <v>0.6965725</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.0339076307476159</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr"/>
       <c r="Q48" t="inlineStr"/>
@@ -2898,9 +2254,6 @@
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
       <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2908,7 +2261,7 @@
           <t>FAR DMC W20-05GrazedNoneCvAccroc</t>
         </is>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C49" t="inlineStr">
@@ -2916,61 +2269,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
+      <c r="D49" t="n">
+        <v>1654.99912237609</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.678072967509678</v>
+      </c>
+      <c r="F49" t="n">
+        <v>454.481161295993</v>
       </c>
       <c r="G49" t="n">
-        <v>1654.99912237609</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.678072967509678</v>
-      </c>
-      <c r="I49" t="n">
-        <v>454.481161295993</v>
-      </c>
-      <c r="J49" t="n">
         <v>22.6371034957693</v>
       </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>75.03100000000001</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.401075637089401</v>
+      </c>
+      <c r="N49" t="n">
+        <v>11.7</v>
+      </c>
       <c r="O49" t="n">
-        <v>75.03100000000001</v>
+        <v>0.0707106781186551</v>
       </c>
       <c r="P49" t="n">
-        <v>0.401075637089401</v>
+        <v>11.775</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.7</v>
+        <v>0.131497781983829</v>
       </c>
       <c r="R49" t="n">
-        <v>0.0707106781186551</v>
+        <v>5.7225</v>
       </c>
       <c r="S49" t="n">
-        <v>11.775</v>
+        <v>0.367885285562407</v>
       </c>
       <c r="T49" t="n">
-        <v>0.131497781983829</v>
+        <v>776.843752436647</v>
       </c>
       <c r="U49" t="n">
-        <v>5.7225</v>
-      </c>
-      <c r="V49" t="n">
-        <v>0.367885285562407</v>
-      </c>
-      <c r="W49" t="n">
-        <v>776.843752436647</v>
-      </c>
-      <c r="X49" t="n">
         <v>0.161689162035359</v>
       </c>
     </row>
@@ -2980,37 +2322,25 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
+      <c r="J50" t="n">
+        <v>0.8432525</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.0115888167177097</v>
+      </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="n">
-        <v>0.8432525</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0.0115888167177097</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr"/>
       <c r="Q50" t="inlineStr"/>
@@ -3018,9 +2348,6 @@
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
       <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3028,37 +2355,25 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="J51" t="n">
+        <v>0.895415</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.00476665064099871</v>
+      </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="n">
-        <v>0.895415</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.00476665064099871</v>
-      </c>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr"/>
       <c r="Q51" t="inlineStr"/>
@@ -3066,9 +2381,6 @@
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
       <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3076,37 +2388,25 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="J52" t="n">
+        <v>0.4144125</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.0257692259536448</v>
+      </c>
       <c r="L52" t="inlineStr"/>
-      <c r="M52" t="n">
-        <v>0.4144125</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.0257692259536448</v>
-      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr"/>
       <c r="Q52" t="inlineStr"/>
@@ -3114,9 +2414,6 @@
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
       <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3124,37 +2421,25 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="J53" t="n">
+        <v>0.70257</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.0223111358593267</v>
+      </c>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="n">
-        <v>0.70257</v>
-      </c>
-      <c r="N53" t="n">
-        <v>0.0223111358593267</v>
-      </c>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr"/>
       <c r="Q53" t="inlineStr"/>
@@ -3162,9 +2447,6 @@
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
       <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3172,37 +2454,25 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>0.817535</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.0175381952226182</v>
+      </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" t="n">
-        <v>0.817535</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.0175381952226182</v>
-      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr"/>
       <c r="Q54" t="inlineStr"/>
@@ -3210,9 +2480,6 @@
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
       <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3220,37 +2487,25 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="n">
+        <v>0.7851875</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.0245632545261548</v>
+      </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="n">
-        <v>0.7851875</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0.0245632545261548</v>
-      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr"/>
       <c r="Q55" t="inlineStr"/>
@@ -3258,9 +2513,6 @@
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
       <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3268,7 +2520,7 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C56" t="inlineStr">
@@ -3276,33 +2528,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="J56" t="n">
+        <v>0.7727475</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.0324208087435112</v>
+      </c>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="n">
-        <v>0.7727475</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.0324208087435112</v>
-      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr"/>
       <c r="Q56" t="inlineStr"/>
@@ -3310,9 +2550,6 @@
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
       <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3320,7 +2557,7 @@
           <t>FAR DMC W20-05GrazedGS30CvAccroc</t>
         </is>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C57" t="inlineStr">
@@ -3328,65 +2565,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>GS30</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D57" t="n">
+        <v>1436.30057582392</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1.16045784758384</v>
+      </c>
+      <c r="F57" t="n">
+        <v>490.384552085025</v>
       </c>
       <c r="G57" t="n">
-        <v>1436.30057582392</v>
-      </c>
-      <c r="H57" t="n">
-        <v>1.16045784758384</v>
-      </c>
-      <c r="I57" t="n">
-        <v>490.384552085025</v>
-      </c>
-      <c r="J57" t="n">
         <v>68.7254998738584</v>
       </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+      <c r="L57" t="n">
+        <v>75.502</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.654271095698616</v>
+      </c>
+      <c r="N57" t="n">
+        <v>12.175</v>
+      </c>
       <c r="O57" t="n">
-        <v>75.502</v>
+        <v>0.0629152869605895</v>
       </c>
       <c r="P57" t="n">
-        <v>0.654271095698616</v>
+        <v>11.05</v>
       </c>
       <c r="Q57" t="n">
-        <v>12.175</v>
+        <v>0.287228132326902</v>
       </c>
       <c r="R57" t="n">
-        <v>0.0629152869605895</v>
+        <v>7.075</v>
       </c>
       <c r="S57" t="n">
-        <v>11.05</v>
+        <v>0.9651381593671799</v>
       </c>
       <c r="T57" t="n">
-        <v>0.287228132326902</v>
+        <v>594.58136849325</v>
       </c>
       <c r="U57" t="n">
-        <v>7.075</v>
-      </c>
-      <c r="V57" t="n">
-        <v>0.9651381593671799</v>
-      </c>
-      <c r="W57" t="n">
-        <v>594.58136849325</v>
-      </c>
-      <c r="X57" t="n">
         <v>0.270020683539231</v>
       </c>
     </row>
@@ -3396,37 +2618,25 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="3" t="n">
         <v>44026</v>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="J58" t="n">
+        <v>0.8488125</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.0136375647722262</v>
+      </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="n">
-        <v>0.8488125</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.0136375647722262</v>
-      </c>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr"/>
       <c r="Q58" t="inlineStr"/>
@@ -3434,9 +2644,6 @@
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
       <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3444,37 +2651,25 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="3" t="n">
         <v>44068</v>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="J59" t="n">
+        <v>0.858555</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.00765327544258011</v>
+      </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="n">
-        <v>0.858555</v>
-      </c>
-      <c r="N59" t="n">
-        <v>0.00765327544258011</v>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr"/>
       <c r="Q59" t="inlineStr"/>
@@ -3482,9 +2677,6 @@
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
       <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3492,37 +2684,25 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="3" t="n">
         <v>44082</v>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
+      <c r="J60" t="n">
+        <v>0.8947475</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.0121361219609066</v>
+      </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" t="n">
-        <v>0.8947475</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.0121361219609066</v>
-      </c>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr"/>
       <c r="Q60" t="inlineStr"/>
@@ -3530,9 +2710,6 @@
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
       <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3540,37 +2717,25 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="3" t="n">
         <v>44097</v>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="n">
+        <v>0.9302375000000001</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.00539196837125984</v>
+      </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="n">
-        <v>0.9302375000000001</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.00539196837125984</v>
-      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr"/>
@@ -3578,9 +2743,6 @@
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
       <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3588,37 +2750,25 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="3" t="n">
         <v>44110</v>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="J62" t="n">
+        <v>0.8708050000000001</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.00214470471938056</v>
+      </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="n">
-        <v>0.8708050000000001</v>
-      </c>
-      <c r="N62" t="n">
-        <v>0.00214470471938056</v>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr"/>
       <c r="Q62" t="inlineStr"/>
@@ -3626,9 +2776,6 @@
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
       <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3636,37 +2783,25 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="3" t="n">
         <v>44139</v>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="J63" t="n">
+        <v>0.83227</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.00678182989072023</v>
+      </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" t="n">
-        <v>0.83227</v>
-      </c>
-      <c r="N63" t="n">
-        <v>0.00678182989072023</v>
-      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr"/>
       <c r="Q63" t="inlineStr"/>
@@ -3674,9 +2809,6 @@
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
       <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3684,7 +2816,7 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="3" t="n">
         <v>44152</v>
       </c>
       <c r="C64" t="inlineStr">
@@ -3692,33 +2824,21 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="J64" t="n">
+        <v>0.740235</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.0337524197897968</v>
+      </c>
       <c r="L64" t="inlineStr"/>
-      <c r="M64" t="n">
-        <v>0.740235</v>
-      </c>
-      <c r="N64" t="n">
-        <v>0.0337524197897968</v>
-      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr"/>
       <c r="Q64" t="inlineStr"/>
@@ -3726,9 +2846,6 @@
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
       <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3736,7 +2853,7 @@
           <t>FAR DMC W20-05GrazedGS22CvAccroc</t>
         </is>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="3" t="n">
         <v>44181</v>
       </c>
       <c r="C65" t="inlineStr">
@@ -3744,65 +2861,50 @@
           <t>HarvestRipe</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Accroc</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>GS22</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
+      <c r="D65" t="n">
+        <v>1825.24133326168</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.46847023769132</v>
+      </c>
+      <c r="F65" t="n">
+        <v>534.291500298962</v>
       </c>
       <c r="G65" t="n">
-        <v>1825.24133326168</v>
-      </c>
-      <c r="H65" t="n">
-        <v>1.46847023769132</v>
-      </c>
-      <c r="I65" t="n">
-        <v>534.291500298962</v>
-      </c>
-      <c r="J65" t="n">
         <v>57.1448697501464</v>
       </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="L65" t="n">
+        <v>74.9945</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.247533667743735</v>
+      </c>
+      <c r="N65" t="n">
+        <v>11.8</v>
+      </c>
       <c r="O65" t="n">
-        <v>74.9945</v>
+        <v>0.122474487139159</v>
       </c>
       <c r="P65" t="n">
-        <v>0.247533667743735</v>
+        <v>11.775</v>
       </c>
       <c r="Q65" t="n">
-        <v>11.8</v>
+        <v>0.125</v>
       </c>
       <c r="R65" t="n">
-        <v>0.122474487139159</v>
+        <v>6.455</v>
       </c>
       <c r="S65" t="n">
-        <v>11.775</v>
+        <v>0.672761721067224</v>
       </c>
       <c r="T65" t="n">
-        <v>0.125</v>
+        <v>770.630236309653</v>
       </c>
       <c r="U65" t="n">
-        <v>6.455</v>
-      </c>
-      <c r="V65" t="n">
-        <v>0.672761721067224</v>
-      </c>
-      <c r="W65" t="n">
-        <v>770.630236309653</v>
-      </c>
-      <c r="X65" t="n">
         <v>0.150842444816427</v>
       </c>
     </row>
